--- a/Houston_Rockets_2025-26_stats.xlsx
+++ b/Houston_Rockets_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +1021,57 @@
       </c>
       <c r="O11" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1621,6 +1672,57 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1635,7 +1737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2223,6 +2325,57 @@
       </c>
       <c r="O11" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2236,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2824,6 +2977,57 @@
       </c>
       <c r="O11" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2859,7 +3063,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.6</v>
+        <v>25.09090909090909</v>
       </c>
     </row>
     <row r="3">
@@ -2869,7 +3073,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.1</v>
+        <v>22.36363636363636</v>
       </c>
     </row>
     <row r="4">
@@ -2879,7 +3083,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.6</v>
+        <v>17.72727272727273</v>
       </c>
     </row>
     <row r="5">
@@ -2889,27 +3093,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.11111111111111</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.3</v>
+        <v>12.27272727272727</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.2</v>
+        <v>11.45454545454546</v>
       </c>
     </row>
     <row r="8">
@@ -2919,7 +3123,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.4</v>
+        <v>8.636363636363637</v>
       </c>
     </row>
     <row r="9">
@@ -2929,47 +3133,47 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.555555555555555</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Clint Capela</t>
+          <t>Aaron Holiday</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.8</v>
+        <v>3.833333333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jeff Green</t>
+          <t>Clint Capela</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>3.636363636363636</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JD Davison</t>
+          <t>Jeff Green</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aaron Holiday</t>
+          <t>JD Davison</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -2979,7 +3183,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.333333333333333</v>
+        <v>1.142857142857143</v>
       </c>
     </row>
   </sheetData>
@@ -3015,7 +3219,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.2</v>
+        <v>7.363636363636363</v>
       </c>
     </row>
     <row r="3">
@@ -3025,7 +3229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6</v>
+        <v>5.454545454545454</v>
       </c>
     </row>
     <row r="4">
@@ -3035,7 +3239,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2</v>
+        <v>3.181818181818182</v>
       </c>
     </row>
     <row r="5">
@@ -3045,33 +3249,33 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2</v>
+        <v>3.181818181818182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Steven Adams</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.777777777777778</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.666666666666667</v>
+        <v>1.636363636363636</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Steven Adams</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -3085,7 +3289,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.3</v>
+        <v>1.272727272727273</v>
       </c>
     </row>
     <row r="10">
@@ -3095,7 +3299,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.2</v>
+        <v>1.166666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -3105,7 +3309,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -3115,7 +3319,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="13">
@@ -3125,7 +3329,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="14">
@@ -3171,7 +3375,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.2</v>
+        <v>10.18181818181818</v>
       </c>
     </row>
     <row r="3">
@@ -3181,7 +3385,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.777777777777779</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3191,7 +3395,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.111111111111111</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -3201,7 +3405,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.1</v>
+        <v>5.727272727272728</v>
       </c>
     </row>
     <row r="6">
@@ -3211,7 +3415,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2</v>
+        <v>5.181818181818182</v>
       </c>
     </row>
     <row r="7">
@@ -3221,7 +3425,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6</v>
+        <v>4.636363636363637</v>
       </c>
     </row>
     <row r="8">
@@ -3231,7 +3435,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5</v>
+        <v>4.454545454545454</v>
       </c>
     </row>
     <row r="9">
@@ -3241,7 +3445,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2</v>
+        <v>2.272727272727273</v>
       </c>
     </row>
     <row r="10">
@@ -3251,7 +3455,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2</v>
+        <v>2.272727272727273</v>
       </c>
     </row>
     <row r="11">
@@ -3261,7 +3465,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="12">
@@ -3271,7 +3475,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -3281,7 +3485,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14">
@@ -3327,7 +3531,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.8</v>
+        <v>2.818181818181818</v>
       </c>
     </row>
     <row r="3">
@@ -3337,7 +3541,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.6</v>
+        <v>2.454545454545455</v>
       </c>
     </row>
     <row r="4">
@@ -3347,7 +3551,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.777777777777778</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3357,27 +3561,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.7</v>
+        <v>1.818181818181818</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Josh Okogie</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>1.545454545454545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Josh Okogie</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.3</v>
+        <v>1.454545454545455</v>
       </c>
     </row>
     <row r="8">
@@ -3387,7 +3591,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -3397,7 +3601,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -3407,7 +3611,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="11">
@@ -3417,7 +3621,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -3461,7 +3665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3701,6 +3905,27 @@
         <v>247</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>140</v>
+      </c>
+      <c r="D12" t="n">
+        <v>116</v>
+      </c>
+      <c r="E12" t="n">
+        <v>256</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
